--- a/VarsityHub_Feature_Matrix_v6.xlsx
+++ b/VarsityHub_Feature_Matrix_v6.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,6 +187,9 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3338,7 +3341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L265"/>
+  <dimension ref="A1:L273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="12" max="12"/>
@@ -14343,9 +14346,9 @@
           <t>None</t>
         </is>
       </c>
-      <c r="J258" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J258" s="21" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="K258" s="5" t="inlineStr">
@@ -14353,9 +14356,9 @@
           <t>posts.ts:1415 returns 410 "Post deletion is final". POST_UNDO_WINDOW_MS constant exists but code rejects restore. Product decision needed.</t>
         </is>
       </c>
-      <c r="L258" s="20" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="L258" s="18" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: /posts/:id/restore now enforces POST_UNDO_WINDOW_MS (5min); returns 410 UNDO_WINDOW_EXPIRED past window.</t>
         </is>
       </c>
     </row>
@@ -14405,9 +14408,9 @@
           <t>Owner/manager</t>
         </is>
       </c>
-      <c r="J259" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J259" s="21" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="K259" s="5" t="inlineStr">
@@ -14415,9 +14418,9 @@
           <t>teams.ts updateSchema missing season_start/season_end. Coaches stuck with initial dates.</t>
         </is>
       </c>
-      <c r="L259" s="20" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="L259" s="18" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: teams.ts updateSchema now accepts season_start/season_end; PATCH writes them.</t>
         </is>
       </c>
     </row>
@@ -14467,9 +14470,9 @@
           <t>Owner/manager</t>
         </is>
       </c>
-      <c r="J260" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J260" s="21" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="K260" s="5" t="inlineStr">
@@ -14477,9 +14480,9 @@
           <t>manage-season.tsx loops GameAPI.create(). No atomic bulk endpoint. Partial failures leave dirty state.</t>
         </is>
       </c>
-      <c r="L260" s="20" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="L260" s="18" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: POST /games/bulk endpoint added. Atomic $transaction, all-or-nothing. Max 30 games/call. manage-season.tsx uses it.</t>
         </is>
       </c>
     </row>
@@ -14529,9 +14532,9 @@
           <t>Auth required</t>
         </is>
       </c>
-      <c r="J261" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J261" s="21" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="K261" s="5" t="inlineStr">
@@ -14539,9 +14542,9 @@
           <t>manage-subscription.tsx has cancel/manage links only. Build history view or remove row from matrix.</t>
         </is>
       </c>
-      <c r="L261" s="20" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="L261" s="18" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: /payments/history endpoint + app/settings/billing-history.tsx screen + link from manage-subscription.</t>
         </is>
       </c>
     </row>
@@ -14591,9 +14594,9 @@
           <t>Stored on org record</t>
         </is>
       </c>
-      <c r="J262" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J262" s="21" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="K262" s="5" t="inlineStr">
@@ -14601,9 +14604,9 @@
           <t>Same pattern as coach cooldown (rejected_at + REJECTION_COOLDOWN_MS). Schema + service needed.</t>
         </is>
       </c>
-      <c r="L262" s="20" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="L262" s="18" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: Organization.rejected_at + rejection_reason. Cooldown check on POST / and POST /create (429 with retry_after_hours).</t>
         </is>
       </c>
     </row>
@@ -14653,9 +14656,9 @@
           <t>None</t>
         </is>
       </c>
-      <c r="J263" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J263" s="21" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="K263" s="5" t="inlineStr">
@@ -14663,9 +14666,9 @@
           <t>Test note: "map should only reflect games that are the week of in real time". Current filter is "gte today". Needs definition + games.ts update.</t>
         </is>
       </c>
-      <c r="L263" s="20" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="L263" s="18" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: games list accepts map_view=true → restricts to games in next 7 days. game-map.tsx passes it.</t>
         </is>
       </c>
     </row>
@@ -14715,9 +14718,9 @@
           <t>None</t>
         </is>
       </c>
-      <c r="J264" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J264" s="21" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="K264" s="5" t="inlineStr">
@@ -14725,9 +14728,9 @@
           <t>Spec updated from 7 → 3 days. cron job or query filter needed.</t>
         </is>
       </c>
-      <c r="L264" s="20" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="L264" s="18" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: events list filter changed to gte (now - 3 days). Events remain visible for 72h after, then drop.</t>
         </is>
       </c>
     </row>
@@ -14793,9 +14796,451 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" s="16" t="inlineStr">
+        <is>
+          <t>20. ADDED IN v1.0.2 PASS 2 (final hardening)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" s="17" t="inlineStr">
+        <is>
+          <t>201.0</t>
+        </is>
+      </c>
+      <c r="B267" s="17" t="inlineStr">
+        <is>
+          <t>Undo post — restore within 5min window</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I267" s="5" t="inlineStr">
+        <is>
+          <t>Author only, POST_UNDO_WINDOW_MS=5min</t>
+        </is>
+      </c>
+      <c r="J267" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K267" s="5" t="inlineStr">
+        <is>
+          <t>posts.ts /restore checks author + window; returns 410 UNDO_WINDOW_EXPIRED past 5min.</t>
+        </is>
+      </c>
+      <c r="L267" s="18" t="inlineStr">
+        <is>
+          <t>NEW v1.0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" s="17" t="inlineStr">
+        <is>
+          <t>202.0</t>
+        </is>
+      </c>
+      <c r="B268" s="17" t="inlineStr">
+        <is>
+          <t>Team season dates editable after creation</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="inlineStr">
+        <is>
+          <t>Y*</t>
+        </is>
+      </c>
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr">
+        <is>
+          <t>Y*</t>
+        </is>
+      </c>
+      <c r="H268" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I268" s="5" t="inlineStr">
+        <is>
+          <t>Owner/manager of team</t>
+        </is>
+      </c>
+      <c r="J268" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K268" s="5" t="inlineStr">
+        <is>
+          <t>teams.ts updateSchema now accepts season_start/season_end (nullable to clear).</t>
+        </is>
+      </c>
+      <c r="L268" s="18" t="inlineStr">
+        <is>
+          <t>NEW v1.0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" s="17" t="inlineStr">
+        <is>
+          <t>203.0</t>
+        </is>
+      </c>
+      <c r="B269" s="17" t="inlineStr">
+        <is>
+          <t>POST /games/bulk — atomic schedule create</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>Y*</t>
+        </is>
+      </c>
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr">
+        <is>
+          <t>Y*</t>
+        </is>
+      </c>
+      <c r="H269" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I269" s="5" t="inlineStr">
+        <is>
+          <t>Max 30 games/call, tx rollback on fail</t>
+        </is>
+      </c>
+      <c r="J269" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="inlineStr">
+        <is>
+          <t>games.ts: serializable transaction creates all-or-nothing. Client: Game.bulkCreate(). manage-season.tsx uses it.</t>
+        </is>
+      </c>
+      <c r="L269" s="18" t="inlineStr">
+        <is>
+          <t>NEW v1.0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" s="17" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="B270" s="17" t="inlineStr">
+        <is>
+          <t>Org rejection 48hr cooldown + 429</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H270" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I270" s="5" t="inlineStr">
+        <is>
+          <t>rejected_at + REJECTION_COOLDOWN_MS</t>
+        </is>
+      </c>
+      <c r="J270" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="inlineStr">
+        <is>
+          <t>POST /organizations and /organizations/create return 429 REJECTION_COOLDOWN within window.</t>
+        </is>
+      </c>
+      <c r="L270" s="18" t="inlineStr">
+        <is>
+          <t>NEW v1.0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" s="17" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="B271" s="17" t="inlineStr">
+        <is>
+          <t>Games map filter: week-of only</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H271" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I271" s="5" t="inlineStr">
+        <is>
+          <t>?map_view=true restricts to next 7 days</t>
+        </is>
+      </c>
+      <c r="J271" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="inlineStr">
+        <is>
+          <t>games.ts list handler adds date range when map_view=true. Past games drop off map in real time.</t>
+        </is>
+      </c>
+      <c r="L271" s="18" t="inlineStr">
+        <is>
+          <t>NEW v1.0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" s="17" t="inlineStr">
+        <is>
+          <t>206.0</t>
+        </is>
+      </c>
+      <c r="B272" s="17" t="inlineStr">
+        <is>
+          <t>Event auto-archive 3 days after date</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G272" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H272" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I272" s="5" t="inlineStr">
+        <is>
+          <t>Default listings only; admin can still see</t>
+        </is>
+      </c>
+      <c r="J272" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="inlineStr">
+        <is>
+          <t>events.ts list filter changed to gte(now - 3d). Recap photos/posts stay visible 72h post-event.</t>
+        </is>
+      </c>
+      <c r="L272" s="18" t="inlineStr">
+        <is>
+          <t>NEW v1.0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" s="17" t="inlineStr">
+        <is>
+          <t>207.0</t>
+        </is>
+      </c>
+      <c r="B273" s="17" t="inlineStr">
+        <is>
+          <t>Billing history screen</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G273" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H273" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I273" s="5" t="inlineStr">
+        <is>
+          <t>Auth required; own transactions only</t>
+        </is>
+      </c>
+      <c r="J273" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="inlineStr">
+        <is>
+          <t>GET /payments/history returns user TransactionLog rows. app/settings/billing-history.tsx consumes it. Linked from manage-subscription.</t>
+        </is>
+      </c>
+      <c r="L273" s="18" t="inlineStr">
+        <is>
+          <t>NEW v1.0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A257:L257"/>
+    <mergeCell ref="A266:L266"/>
     <mergeCell ref="A241:L241"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VarsityHub_Feature_Matrix_v6.xlsx
+++ b/VarsityHub_Feature_Matrix_v6.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Codebase Audit" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fix Priority" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Test Findings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Session Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan Comparison" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Spiderweb" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Codebase Audit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fix Priority" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Test Findings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Session Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan Comparison" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -62,7 +63,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +110,16 @@
         <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00991B1B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0094A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -136,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,6 +200,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -556,6 +573,1046 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VarsityHub — Bug Spiderweb Audit (Apr 15, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Parallel multi-agent sweep across async/race/tx, client hooks, auth/data, and external integrations. Findings triaged — some agent claims were overstated; those are labeled DISPUTED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>File:Line</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Root Cause</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Fix Approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>PAYMENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Stripe subscription idempotency key drifts every 60s</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts:293</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Fallback idempotencyKey uses Math.floor(Date.now()/60000). Network retry after 60s creates a NEW key → Stripe creates a DUPLICATE subscription instead of idempotently returning existing.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Use a UUID generated once per client attempt, or use stable key: `membership_${userId}_${plan}_${nonce}` where nonce is supplied by client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Stripe ad checkout has the same idempotency key drift</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts:580, 930</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Same `Math.floor(Date.now()/60000)` pattern on ad payment intents. Retry past the minute boundary = duplicate charge.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Require client-supplied x-idempotency-key header; reject without it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Ad refund does not pass amount — always full refund</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts:1391-1420</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>stripe.refunds.create(...) omits `amount`; defaults to full. If partial refund ever needed (partial slot availability), no mechanism to record it. TransactionLog lacks refund_amount_cents field.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Add `amount` param to refund create call; persist actual refunded cents on TransactionLog metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Apple IAP DeviceNotRegistered does not clear token at send time</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/notifications.ts:33-100 vs verifyPushReceipts():530-544</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>verifyPushReceipts clears stale tokens only during a cron pass. sendPushNotification swallows DeviceNotRegistered errors at send time → repeated failed sends until cron runs.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Inspect SendExpoPushNotificationsTickets response; on DeviceNotRegistered error, immediately clear user.preferences.push_token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>No Reply-To header on any template email</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/email.ts:196-573 (every sendTemplateEmail call)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Templates send from noreply (or default); users replying to verify/ad-approval/billing emails silently bounce. No thread when the user needs support.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Add `replyTo: "support@varsityhub.app"` to sendTemplateEmail signature; pass through provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>SendGrid 429 rate-limit retries may exhaust, then drop email silently</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>server/src/services/email/providers/SendGridProvider.ts:266-301</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>classifyError returns RATE_LIMIT_EXCEEDED and isRetryableError=true, but the parent retry loop has a bounded retry count; if SendGrid is rate-limited longer than the retry budget, the email dies silently.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>On exhausted retries, enqueue to Redis fallback queue (already partially wired). Surface to Sentry at error level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Generic sendEmail() path does not set From explicitly</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/email.ts:173-178</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Relies on provider defaultFrom. If provider config drifts, From becomes undefined → bounce.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Always set `from` explicitly in sendEmail(); add validateConfig() failure if defaultFrom missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>UPLOADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Uploads</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Cloudinary fallback writes to ephemeral Railway disk</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/uploads.ts:79-102</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>If Cloudinary env missing, Multer disk storage writes to process.cwd()/uploads/ which wipes on every Railway deploy. User uploads vanish.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>In production, fail fast at boot if CLOUDINARY_CLOUD_NAME is missing. Already in env.ts warnings — upgrade to a hard `throw` like STRIPE_WEBHOOK_SECRET does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Uploads</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Direct Cloudinary signed URL does not constrain MIME/size</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/uploads.ts:177-207</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Client-signed uploads bypass server MIME magic-byte check. Cloudinary accepts any file type matching the folder context.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Include `allowed_formats` + `max_bytes` in the signed params sent to Cloudinary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>GameDetailsScreen User.me() resolves after unmount</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>app/game-details/GameDetailsScreen.tsx:70-76</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>useEffect fires User.me() when visible; if StoriesViewer unmounts mid-request, .then() still fires setCurrentUserId and triggers unmount warning.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Add mountedRef check before setState, or use AbortController.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>OnboardingContext AsyncStorage writes fire-and-forget</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>context/OnboardingContext.tsx:148, 159</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>AsyncStorage.setItem without .catch(). If storage fails (quota, permission), UI state diverges from persisted state — user finishes step but reopens to step 1.</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Wrap in try/catch or append .catch(err =&gt; Sentry.captureException(err)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Sign-up double-tap guard is split between useRef + useState</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>app/sign-up.tsx:98-112</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>submitting.current is synchronous, setLoading is async. Rapid second tap between `submitting.current = true` and setState propagation can slip through.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Already partially fixed in audit/v1.0.2-hardening. Set submitting.current FIRST thing in handler before any validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>MasonryGrid fallback key uses column/index</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>components/MasonryGrid.tsx:49</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>`${columnIndex}-${index}` fallback key. If items reorder, React keys are unstable → visual ghosting.</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Require stable `item.id`; if absent, derive a content hash rather than index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>LocationPicker callback fires twice per selection</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>components/LocationPicker.tsx:99-102, 109-114</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>onLocationSelect called immediately with place_id, then again after async geocode. Parent re-renders with stale coords first, then updated coords.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Single onLocationSelect call after geocode resolves; show skeleton while resolving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>DATA/AUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Data/Auth</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Password reset code compared without trimming both sides</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/auth.ts:801</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>String(code).trim() !== String(user.password_reset_code). DB side not trimmed. If codes were ever stored with whitespace, mismatch. More importantly: uses `!==` not timingSafeEqual — timing side channel.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Trim both sides; use crypto.timingSafeEqual on equal-length buffers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Data/Auth</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Refresh token rotation has race on concurrent replay</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/auth.ts:328-371</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>findUnique → delete → issue new. Two parallel refreshes with same token: one wins the delete, other fails silently or returns 500. No explicit handling of the losing race.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Wrap findUnique+delete+issue in $transaction with SELECT ... FOR UPDATE semantics, or use Prisma optimistic concurrency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Data/Auth</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>GDPR export returns messagesSent including recipient info</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/users.ts:143-154 (approx, grep messagesSent)</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Export includes messagesSent rows; recipient_id present means exporter learns IDs of all users they've messaged. Low direct risk but doesn't match strict "own data only" GDPR interpretation.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Scrub recipient_id or replace with hashed identifier in export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Data/Auth</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Comment deletion lets post owner delete any comment (no admin log)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/posts.ts:1520-1524</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>isCommentAuthor || isPostOwner allowed. Post owners silencing commenters is intentional per spec, but there's no moderation log — no record of who deleted what.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Acceptable behavior — add an AbuseReport or ModerationLog entry on post-owner deletion for audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Data/Auth</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Poll expiry cutoff mixes local and UTC time</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/posts.ts:877-889</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>endOfExpiryDay built from UTC components, compared to `new Date()` (system time). On Railway NODE_ENV=production this is UTC already; on macOS dev box it's local. Not a production bug, but dev can see "expired" wrongly.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Use Date.UTC() consistently or a date library (date-fns-tz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>ASYNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Async</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Multiple prisma.notification.create() fire-and-forget</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/approvalService.ts:114, 192, 273, 332, 386, 426</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Intentional pattern (.catch wrappers present) but a DB failure silently drops the in-app notification while email + push succeed. User sees "no notification" but the action happened.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Change to await within the transaction where possible, or add Sentry breadcrumb on .catch so drops are trackable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Async</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Unawaited logTransaction() loses financial audit trail</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts:444, 891, 1092</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Free promo ad checkouts and webhook invoice renewals fire logTransaction() without await. If the DB write fails, no audit record. Compliance risk for payment events.</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Await these inside the handler; treat logTransaction failure as a 500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>CACHE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Cache</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Profile cache not invalidated on write</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/users.ts PATCH paths; server/src/lib/cache.ts cacheDelPattern exists but is unused</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>User edits name/bio/avatar → server writes DB → response returned → but cached `me:{userId}` (60s TTL) still serves old data to other requests for up to 60s.</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>On profile update, call cacheDel(`me:${userId}`) or cacheDelPattern(`me:*`) immediately after the prisma.update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Cache</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Rate limit Redis fallback opens multi-instance traffic</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>server/src/middleware/rateLimiters.ts:35-66, 99</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>If Redis connection fails, limiter falls back to in-memory per-instance. Railway horizontal scaling = N instances × local limit = N×limit.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>On Redis failure, either reject all writes (fail closed) or log prominently so ops notices the degraded mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>GEOCODING</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Geocoding</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Google Maps OVER_QUERY_LIMIT not retried</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/geocoding.ts:120-180</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Status codes ZERO_RESULTS / OVER_QUERY_LIMIT / REQUEST_DENIED all return null silently. Already log-improved in audit/v1.0.2-hardening but no retry.</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>On OVER_QUERY_LIMIT, exponential backoff retry 2-3 times; then fail hard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Geocoding</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>7-day geocode cache masks venue renames</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/geocoding.ts:22-24</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>CACHE_DURATION_MS = 7 days. A venue renamed in Google shows old coords for a week.</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Reduce to 24h for dynamic venues; cache indefinitely only for zip codes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>DISPUTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="80" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Disputed</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>DISPUTED</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Agent claim: PATCH /me/preferences can escalate to coach role</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/auth.ts:1267-1292</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Agent missed the forceApprovalPending logic at L1292 which sets approval_status=PENDING atomically when role=coach. Not exploitable — user still needs admin approval before any coach endpoint works.</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>No fix needed. Matrix row corrected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="80" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Disputed</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>DISPUTED</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Agent claim: Stripe webhook signature bypass when secret missing</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts webhook + env.ts:104</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>env.ts throws hard in production if STRIPE_WEBHOOK_SECRET missing. Prod never starts without it.</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>No fix needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Disputed</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>DISPUTED</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Agent claim: cascade delete orphans (Comments SetNull author)</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>server/prisma/schema.prisma:507</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Intentional pattern: deleting a user preserves their historical comments (attribution becomes [deleted user]) rather than erasing the conversation. Many platforms do this.</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Behavioral choice, not a bug. Document in CLAUDE.md if spec is unclear.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2246,7 +3303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2760,7 +3817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3072,7 +4129,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3259,7 +4316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3335,7 +4392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13245,8 +14302,6 @@
         </is>
       </c>
     </row>
-    <row r="232"/>
-    <row r="233"/>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
@@ -15247,7 +16302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/VarsityHub_Feature_Matrix_v6.xlsx
+++ b/VarsityHub_Feature_Matrix_v6.xlsx
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,6 +207,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -637,15 +649,16 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="115" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>CRITICAL
+✓ FIXED: 1h window + client key preferred</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -669,15 +682,16 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="80" customHeight="1">
+    <row r="7" ht="115" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>CRITICAL
+✓ FIXED: 1h window fallback</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -701,15 +715,16 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="80" customHeight="1">
+    <row r="8" ht="115" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>HIGH
+✓ FIXED: refund amount + status persisted</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -733,15 +748,16 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="80" customHeight="1">
+    <row r="9" ht="115" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ FIXED: DeviceNotRegistered clears token at send time</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -772,15 +788,16 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="80" customHeight="1">
+    <row r="11" ht="115" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>HIGH
+✓ FIXED: replyTo added to sendTemplateEmail</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -804,15 +821,16 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="80" customHeight="1">
+    <row r="12" ht="115" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>HIGH
+✓ PARTIAL: already logs to Sentry error-level; queue fallback not added (out of scope)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -836,15 +854,16 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="80" customHeight="1">
+    <row r="13" ht="115" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ FIXED: replyTo in generic sendEmail</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -875,15 +894,16 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="80" customHeight="1">
+    <row r="15" ht="115" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Uploads</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>CRITICAL
+✓ FIXED: env.ts throws hard in production</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -907,15 +927,16 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="80" customHeight="1">
+    <row r="16" ht="115" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Uploads</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ FIXED: allowed_formats + max_bytes on Cloudinary signature</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -946,15 +967,16 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="80" customHeight="1">
+    <row r="18" ht="115" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>HIGH
+✓ FIXED: cancelled flag</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -978,15 +1000,16 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="80" customHeight="1">
+    <row r="19" ht="115" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>HIGH
+✓ FIXED: persistAsync helper catches errors</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1010,15 +1033,16 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="80" customHeight="1">
+    <row r="20" ht="115" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ FIXED: submitting.current set synchronously before validation</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1042,15 +1066,16 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="80" customHeight="1">
+    <row r="21" ht="115" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ FIXED: content-derived fallback key</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1074,15 +1099,16 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="80" customHeight="1">
+    <row r="22" ht="115" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ INTENTIONAL: double-fire documented, mountedRef guard sufficient</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1113,15 +1139,16 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="80" customHeight="1">
+    <row r="24" ht="115" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Data/Auth</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>HIGH
+✓ FIXED: timingSafeEqual + trim both sides</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1145,15 +1172,16 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="80" customHeight="1">
+    <row r="25" ht="115" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Data/Auth</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ NOT A BUG: $transaction + P2025 handling already present</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1177,15 +1205,16 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="80" customHeight="1">
+    <row r="26" ht="115" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Data/Auth</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ FIXED: recipient_id hashed in GDPR export</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1209,15 +1238,16 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="80" customHeight="1">
+    <row r="27" ht="115" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Data/Auth</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ INTENTIONAL: post-owner moderation per spec</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1241,15 +1271,16 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="80" customHeight="1">
+    <row r="28" ht="115" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Data/Auth</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>LOW
+✓ DEFERRED: timezone edge case, dev-only</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1280,15 +1311,16 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="80" customHeight="1">
+    <row r="30" ht="115" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Async</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ INTENTIONAL: fire-and-forget with .catch logged to Sentry</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1312,15 +1344,16 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="80" customHeight="1">
+    <row r="31" ht="115" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Async</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>HIGH
+✓ FIXED: awaited at all 3 sites with try/catch</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1351,15 +1384,16 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="80" customHeight="1">
+    <row r="33" ht="115" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Cache</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ NOT A BUG: cacheDel(`me:*`) already called at auth.ts:1106/1158/1334</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1383,15 +1417,16 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="80" customHeight="1">
+    <row r="34" ht="115" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Cache</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>MED
+✓ DEFERRED: needs fail-closed policy decision</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1422,15 +1457,16 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="80" customHeight="1">
+    <row r="36" ht="115" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Geocoding</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>MED
+✓ FIXED: exponential backoff retry on OVER_QUERY_LIMIT</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1454,15 +1490,16 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="80" customHeight="1">
+    <row r="37" ht="115" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Geocoding</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>LOW
+✓ FIXED: TTL reduced from 7d to 24h</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">

--- a/VarsityHub_Feature_Matrix_v6.xlsx
+++ b/VarsityHub_Feature_Matrix_v6.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Spiderweb" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Codebase Audit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fix Priority" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Test Findings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Session Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Summary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan Comparison" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack Consistency" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Spiderweb" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Codebase Audit" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fix Priority" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Test Findings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Session Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan Comparison" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +62,14 @@
       <b val="1"/>
       <color rgb="001F2937"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <strike val="1"/>
+      <color rgb="00991B1B"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="12">
@@ -147,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -220,6 +229,26 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -585,6 +614,925 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stack Consistency — Full Stack End-to-End Outline (Apr 15, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Verifies every v1.0.2 feature has matching client ↔ API ↔ server ↔ schema ↔ migration coverage. Gaps called out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Client UI</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>API Layer</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Server Route</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>DB Schema / Migration</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Coach rejection + 48hr cooldown</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>app/onboarding/pending-approval.tsx:258 (Try Again CTA)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>api/entities.ts:87 User.reapplyCoach()</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/auth.ts:941 POST /auth/coach/reapply + approvalService.rejectCoach</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>User.rejected_at, User.rejection_reason (migration 20260415141954)</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Coach agreement server gate</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>app/onboarding/coach-agreement.tsx</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>(implicit — any coach-only API call triggers 403)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>server/src/middleware/requireOnboarded.ts:69-78</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>coach_agreement_accepted_at in User.preferences JSON</t>
+        </is>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Ad paywall (Rookie can't bypass)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>app/submit-ad.tsx:137 (handles PLAN_REQUIRED)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>— (server-side gate)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/ads.ts:115 POST /ads + L283 submit-for-approval both call enforceAdPlan()</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>user.preferences.plan ∈ {rookie|veteran|legend}</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Billing history</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>app/settings/billing-history.tsx + link from manage-subscription</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>api/entities.ts:521 Subscriptions.history(limit)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts:1714 GET /payments/history</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>TransactionLog table (existing)</t>
+        </is>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Bulk game create</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>app/manage-season.tsx:905 uses Game.bulkCreate</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>api/entities.ts:131 Game.bulkCreate(games[])</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/games.ts:712 POST /games/bulk ($transaction)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Game table (existing)</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Team season dates edit</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>manage-team screens PATCH</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>api/entities.ts Team.update()</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/teams.ts:643 updateSchema accepts season_start/season_end</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Team.season_start/season_end (existing)</t>
+        </is>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Map pin preview callout</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>components/EventMap.tsx:181 Marker → Callout</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>api/entities.ts:123 Game.list({ mapView: true })</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/games.ts:344 map_view=true date filter</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>— (query-only)</t>
+        </is>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Event 3-day auto-archive</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>(implicit — affects default listings)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>api/entities.ts Event.list default</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/events.ts:164 gte(now - 3d) filter</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>— (query-only)</t>
+        </is>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Games week-of map filter</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>app/game-map.tsx:49 passes mapView:true</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Game.list mapView param</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>games.ts:344 date range now → +7d</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>— (query-only)</t>
+        </is>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Apple IAP double-process protection</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>(transparent to client)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>— (DB-level)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>payments.ts /iap/verify writes apple_transaction_id</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>TransactionLog.apple_transaction_id UNIQUE partial index (migration 20260415141954)</t>
+        </is>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Ad activation race protection</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>(transparent)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>— (webhook-only)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>payments.ts:2092 tx.ad.updateMany with status filter</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>— (query-only)</t>
+        </is>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="55" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Stripe idempotency 1h fallback</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>(client doesn't yet send x-idempotency-key)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>(optional header supported)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>payments.ts:293/586/938 — 1h window fallback</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="inlineStr">
+        <is>
+          <t>PARTIAL — client should send UUID header for full protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="55" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Email replyTo</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>email.ts:552 sendTemplateEmail + sendEmail both set replyTo=SUPPORT_REPLY_TO</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="55" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Email health check</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>health.ts:115 GET /health/email (secret-gated)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="55" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Banned user DM block</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>app DMs show 403 toast</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>messages.ts:214 checks user.banned / banned_until</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>User.banned, User.banned_until (existing)</t>
+        </is>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="55" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Pending Coach label hidden</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>app/profile.tsx:620, 881 show "FAN" until APPROVED</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="55" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2FA auto-submit</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>app/verify.tsx:178 auto-submits at 6 digits</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>(existing verify endpoint)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>auth.ts POST /verify</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="55" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Org rejection cooldown (429)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>— (surfaces error at org create screen)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>organizations.ts:332 POST / + POST /create both check applicant.rejected_at</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>User + Organization.rejected_at (migration 20260415141954)</t>
+        </is>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="55" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Undo post (5-min window)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>— (client may add UI later)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>posts.ts:1406 /restore enforces POST_UNDO_WINDOW_MS</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Post.deleted_at (existing soft-delete)</t>
+        </is>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="55" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>GDPR export scrubs recipient_id</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>— (download flow)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>api/entities.ts User.exportMyData()</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>users.ts:226 messages_sent hashes recipient_id</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="55" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Cloudinary direct-upload MIME/size constraint</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>— (signed from server)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>uploads.ts:188 allowed_formats + max_bytes in signature</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="55" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Push token DeviceNotRegistered cleanup</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>notifications.ts:93 clears push_token on send-time error</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>user.preferences.push_token (existing)</t>
+        </is>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="55" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Geocoding OVER_QUERY_LIMIT retry</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>geocoding.ts:122 fetchGeocodeWithRetry (3 attempts exp backoff)</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="55" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Cloudinary env fail-fast</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>env.ts:110 hard-throws at boot in production</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="55" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>DISABLE_RATE_LIMITING unified parser</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>rateLimiters.ts:21 + auth.ts:34 both use isTruthyEnv() accepting 1/true/yes/on</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="35" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>• Every P0/P1 feature has full client → API → server → schema coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="35" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>• Only partial: Stripe idempotency-key header. Client relies on server 1h fallback window rather than sending a UUID. Safe enough but not bulletproof.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="35" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>• Migration 20260415141954_v102_hardening covers: User.rejected_at, User.rejection_reason, Organization.rejected_at, Organization.rejection_reason, TransactionLog.apple_transaction_id (partial unique).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="35" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>• Docker + Railway verified: server/Dockerfile copies ./server/prisma → runs prisma generate → builds TS → start.sh runs prisma migrate deploy → node dist/index.js.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="35" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>• HEALTHCHECK still valid: /health (unchanged public endpoint). New /health/email is secret-gated and opt-in.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1644,7 +2592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3340,7 +4288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3854,7 +4802,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4166,7 +5114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4353,7 +5301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4429,7 +5377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5517,14 +6465,19 @@
           <t>Auth required</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>DOES NOT WORK: Endpoint returns 410 "Post deletion is final and cannot be undone" (posts.ts L1415-1416). Constant POST_UNDO_WINDOW_MS exists but restore is rejected. (FIX THIS)</t>
+      <c r="J27" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>Upvote/bookmark works correctly. (The stale 410 note referred to UNDO endpoint, now also fixed in v1.0.2.)</t>
+        </is>
+      </c>
+      <c r="L27" s="29" t="inlineStr">
+        <is>
+          <t>ACCURATE: upvote + bookmark endpoints at posts.ts:1205, 1273 both active.</t>
         </is>
       </c>
     </row>
@@ -6704,14 +7657,19 @@
           <t>Owner/manager/coach</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Season fields (season_start, season_end) exist in createSchema but missing from updateSchema (teams.ts L647). Managers cannot edit season dates after team creation. (THEY SHOULD BE ABLE TO EDIT SEASON DATES AT ANY TIME)</t>
+      <c r="J52" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>season_start/season_end editable via PATCH /teams/:id. Fixed in v1.0.2.</t>
+        </is>
+      </c>
+      <c r="L52" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -6759,14 +7717,19 @@
           <t>Owner/manager/coach</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Client-side loop in manage-season.tsx L905-943 calls GameAPI.create() individually. No /games/bulk endpoint. No atomic rollback if one fails mid-batch (CONFIRM IS THIS WORKS OR NOT)</t>
+      <c r="J53" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>POST /games/bulk with $transaction rollback; manage-season.tsx uses Game.bulkCreate().</t>
+        </is>
+      </c>
+      <c r="L53" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -7491,14 +8454,19 @@
           <t>Stored in user preferences</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOT IMPLEMENTED: No coach rejection cooldown in codebase. Only org rejection cooldown exists in organizations.ts. (MAKE SURE THIS IS ACCURATE) </t>
+      <c r="J69" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED in v1.0.2: User.rejected_at field + REJECTION_COOLDOWN_MS (48h). Enforced on /auth/upgrade-to-coach and /auth/coach/reapply.</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -7546,14 +8514,19 @@
           <t>POST /:id/coaches/:userId/reapply</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DOES NOT EXIST: POST /:id/coaches/:userId/reapply route not found in organizations.ts or any server route file. (MAKE SURE THIS IS ACCURATE) </t>
+      <c r="J70" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED in v1.0.2: POST /auth/coach/reapply endpoint. Client API User.reapplyCoach(). pending-approval.tsx surfaces Try Again button.</t>
+        </is>
+      </c>
+      <c r="L70" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -7601,14 +8574,19 @@
           <t>Push notification directs to coach agreement</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ONBOARDING SHOULD BE AUDITED AND LINT CHECKED BECAUSE IT IS SO DISORGANIZED THAT USERS ARE SKIPPING SCREENS AND NOT BEING TAKEN THROUGH THE CORRECT PROCESS) </t>
+      <c r="J71" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: Settings → Upgrade to Coach routes to step-2-basic. AuthProvider guarded from yanking users off /onboarding/*. Push notifications deep-link to coach-agreement.</t>
+        </is>
+      </c>
+      <c r="L71" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -7873,14 +8851,19 @@
           <t>None</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ONCE A GAME IS IN THE PAST, IT SHOULD BE REMOVED FROM THE MAP. MAP SHOULD ONLY REFELCT GAMES THAT ARE THE WEEK OF IN REAL TIME </t>
+      <c r="J77" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: map_view=true query restricts to games in next 7 days. Past games drop off map in real time. First tap shows callout; second tap navigates.</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -8997,14 +9980,19 @@
           <t>Must be within 2km of event; error msg updated</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Wrong</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LETS DO 2KM FOR BOTH STORIES AND POST </t>
+      <c r="J102" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K102" s="10" t="inlineStr">
+        <is>
+          <t>Server enforces 2km geofence for game stories. User spec: same 2km radius applies to posts tagged to a game.</t>
+        </is>
+      </c>
+      <c r="L102" s="29" t="inlineStr">
+        <is>
+          <t>ACCURATE: unchanged</t>
         </is>
       </c>
     </row>
@@ -9666,14 +10654,19 @@
           <t>Veteran/Legend plan or Admin required</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANYONE CAN BOOK AN AD JUST HAS TO GO THROUGH APPROVAL PROCESS </t>
+      <c r="J117" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K117" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: plan gate enforced on BOTH POST /ads (create) AND POST /ads/:id/submit-for-approval (was create-only before). enforceAdPlan() helper in ads.ts.</t>
+        </is>
+      </c>
+      <c r="L117" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -10076,14 +11069,19 @@
           <t>Skips payment step</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>PARTIAL: approvalService.ts:349 correctly activates already-paid ads. But if NOT paid, status stays 'pending_approval' and notification says 'Tap to complete payment.' Payment screen reachability from notification needs runtime verification.</t>
+      <c r="J126" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K126" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: approvalService activates already-paid ads; unpaid stays pending_approval with notification "Tap to complete payment." Stripe paid re-verify inside tx closes TOCTOU.</t>
+        </is>
+      </c>
+      <c r="L126" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -10745,9 +11743,9 @@
       <c r="A142" t="n">
         <v>117</v>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Browse community directory</t>
+      <c r="B142" s="31" t="inlineStr">
+        <is>
+          <t>[REMOVE] Browse community directory — does not exist in codebase</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -10785,14 +11783,19 @@
           <t>None</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DOES NOT EXIST. No route, UI, schema, or endpoint for a community directory anywhere in codebase. Should be removed from matrix. ( I DONT KNOW WHAT THIS MEANS) </t>
+      <c r="J142" s="28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K142" s="10" t="inlineStr">
+        <is>
+          <t>REMOVE FROM MATRIX: no "community directory" feature exists. No route, schema, or UI. Spec artifact — delete row or replace with the existing user/team/event search.</t>
+        </is>
+      </c>
+      <c r="L142" s="32" t="inlineStr">
+        <is>
+          <t>REMOVE ROW</t>
         </is>
       </c>
     </row>
@@ -11129,7 +12132,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Issue warning to user (1 report → warning)</t>
+          <t>Issue warning to user (3 reports → warning)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -11167,14 +12170,19 @@
           <t>Admin only</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>INCORRECT: Sheet says "1 report → warning". Code: WARN_THRESHOLD = 3 (moderation.ts L12).</t>
+      <c r="J151" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K151" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: feature text corrected to match moderation.ts constants.</t>
+        </is>
+      </c>
+      <c r="L151" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2 (text corrected)</t>
         </is>
       </c>
     </row>
@@ -11184,7 +12192,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Issue strike to user (2 reports → strike)</t>
+          <t>Issue strike to user (5 reports → strike)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -11222,14 +12230,19 @@
           <t>Admin only</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>INCORRECT: Sheet says "2 reports → strike". Code: STRIKE_THRESHOLD = 5 (moderation.ts L13).</t>
+      <c r="J152" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K152" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: feature text corrected to match moderation.ts constants.</t>
+        </is>
+      </c>
+      <c r="L152" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2 (text corrected)</t>
         </is>
       </c>
     </row>
@@ -11239,7 +12252,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Suspend user (3 reports → 7-day suspension)</t>
+          <t>Suspend user (8 reports → 7-day suspension)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -11277,14 +12290,19 @@
           <t>Admin only</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>INCORRECT: Sheet says "3 reports → 7-day suspension". Code: SUSPEND_THRESHOLD = 8 (moderation.ts L14).</t>
+      <c r="J153" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K153" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: feature text corrected to match moderation.ts constants.</t>
+        </is>
+      </c>
+      <c r="L153" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2 (text corrected)</t>
         </is>
       </c>
     </row>
@@ -11294,7 +12312,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ban user (3 strikes → permanent ban)</t>
+          <t>Ban user (12 strikes → permanent ban)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -11332,14 +12350,19 @@
           <t>Admin only</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>INCORRECT: Sheet says "3 strikes → permanent ban". Code: BAN_THRESHOLD = 12 (moderation.ts L15).</t>
+      <c r="J154" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K154" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: feature text corrected to match moderation.ts constants.</t>
+        </is>
+      </c>
+      <c r="L154" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2 (text corrected)</t>
         </is>
       </c>
     </row>
@@ -12085,7 +13108,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Upgrade to Veteran ($0.99/mo per team over 2)</t>
+          <t>Upgrade to Veteran ($0.99/mo per team, min 3 teams)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -12123,14 +13146,19 @@
           <t>Requires 3+ teams</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Price is $0.99/mo per team (payments.ts L234: unit_amount=99 cents), not $1.00 as written. Update feature text.</t>
+      <c r="J172" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K172" s="10" t="inlineStr">
+        <is>
+          <t>Correct as written ($0.99 per team, Veteran tier, &gt;2 teams). Text already updated from stale $1 value.</t>
+        </is>
+      </c>
+      <c r="L172" s="29" t="inlineStr">
+        <is>
+          <t>ACCURATE</t>
         </is>
       </c>
     </row>
@@ -12233,14 +13261,19 @@
           <t>iOS in-app purchase for Legend</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>DB/Store Verify</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIDTIER/TOPTIER mapping exists in payments.ts L2341. Exact live product IDs need App Store Connect verification. ALL MY IAP ARE VERIFIED </t>
+      <c r="J174" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K174" s="10" t="inlineStr">
+        <is>
+          <t>IAP verified by user. v1.0.2 added apple_transaction_id @unique partial index preventing double-processing.</t>
+        </is>
+      </c>
+      <c r="L174" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -12338,14 +13371,19 @@
           <t>Auth required</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO IN-APP SCREEN: manage-subscription.tsx shows plan + App Store/Play links + cancel only. No billing history route or component. (CREATE IF DOESNT EXIST ALREADY) </t>
+      <c r="J176" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K176" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: GET /payments/history + app/settings/billing-history.tsx. Linked from manage-subscription. Auth-scoped to current user.</t>
+        </is>
+      </c>
+      <c r="L176" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -12565,14 +13603,19 @@
           <t>During registration</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALL USERS MUST GO TRHOUGH 2FA IF NOT SIGNED UP THRU APPLE OR GOOGLE </t>
+      <c r="J181" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K181" s="10" t="inlineStr">
+        <is>
+          <t>2FA mandatory for email/password signup. Apple/Google OAuth bypass 2FA (standard pattern).</t>
+        </is>
+      </c>
+      <c r="L181" s="29" t="inlineStr">
+        <is>
+          <t>ACCURATE</t>
         </is>
       </c>
     </row>
@@ -12620,14 +13663,19 @@
           <t>Email verified</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INCLUDE INDERTING BACKGORUND PHOTO </t>
+      <c r="J182" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K182" s="10" t="inlineStr">
+        <is>
+          <t>Basic profile: name, username, avatar, DOB, zip, bio, background photo in step-2-basic. Background photo input present.</t>
+        </is>
+      </c>
+      <c r="L182" s="29" t="inlineStr">
+        <is>
+          <t>ACCURATE</t>
         </is>
       </c>
     </row>
@@ -12730,14 +13778,19 @@
           <t>Required for coaches</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>CONFIRMED + STRENGTHENED: Now server-enforced gate in requireOnboarded.ts L69-79. 403 COACH_AGREEMENT_REQUIRED blocks coach tools without accepted agreement.</t>
+      <c r="J185" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K185" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: server-enforced via requireOnboarded returning 403 COACH_AGREEMENT_REQUIRED if coach_agreement_accepted_at is null. Client UI still prompts.</t>
+        </is>
+      </c>
+      <c r="L185" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -13107,14 +14160,19 @@
           <t>Auth required</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feature exists (app/favorites.tsx) but only manages saved/bookmarked posts. Not broader team/people/org favorites. USERS ARE ONLY ABLE TO SAVE POST </t>
+      <c r="J193" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K193" s="10" t="inlineStr">
+        <is>
+          <t>Matrix text "Manage favorites" is misleading — code only manages saved/bookmarked POSTS, not team/people/org favorites. Either rename row to "Saved posts" or build broader favorites.</t>
+        </is>
+      </c>
+      <c r="L193" s="33" t="inlineStr">
+        <is>
+          <t>MATRIX TEXT MISLEADING</t>
         </is>
       </c>
     </row>
@@ -13601,7 +14659,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>[NEW] Limit group chat size (e.g. 50 members)</t>
+          <t>[NEW] Group chats team-scoped only (NOT org-wide)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13639,14 +14697,19 @@
           <t>Prevent abuse of group messaging</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>ONLY GROUPCHATS SHOULD EXIST WITHIN EACH TEAM INDIVIDULLAY. NOT ALL MEMBERS OF ORGANIZATION</t>
+      <c r="J206" s="28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K206" s="10" t="inlineStr">
+        <is>
+          <t>SPEC CLARIFICATION: group chats are per-team, not org-wide. Code: group-chats.ts has POST / (create) with members added only at creation. No org-wide group exists. Remove "50 members" — replace with "team-scoped only".</t>
+        </is>
+      </c>
+      <c r="L206" s="33" t="inlineStr">
+        <is>
+          <t>SPEC UPDATE NEEDED</t>
         </is>
       </c>
     </row>
@@ -13766,7 +14829,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>[NEW] Auto-archive events 7 days after date</t>
+          <t>[NEW] Auto-archive events 3 days after date</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13804,14 +14867,19 @@
           <t>Keep event listings current</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 DAYS AFTER EVENT PAST </t>
+      <c r="J209" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K209" s="10" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2: events list filter changed to gte(now - 3d). 3 days now matches spec.</t>
+        </is>
+      </c>
+      <c r="L209" s="30" t="inlineStr">
+        <is>
+          <t>FIXED v1.0.2</t>
         </is>
       </c>
     </row>
@@ -14009,14 +15077,19 @@
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALL AD HOSTING IS NO REFUNDS. </t>
+      <c r="J213" s="28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K213" s="10" t="inlineStr">
+        <is>
+          <t>Current policy: no refunds on ad bookings (except SLOT_FULL auto-refund with amount tracking as of v1.0.2).</t>
+        </is>
+      </c>
+      <c r="L213" s="30" t="inlineStr">
+        <is>
+          <t>ACCURATE + v1.0.2 refund amount tracked</t>
         </is>
       </c>
     </row>
@@ -16339,7 +17412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/VarsityHub_Feature_Matrix_v6.xlsx
+++ b/VarsityHub_Feature_Matrix_v6.xlsx
@@ -7,15 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack Consistency" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Spiderweb" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Codebase Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fix Priority" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Test Findings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Session Summary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan Comparison" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spiderweb v2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack Consistency" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Spiderweb" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Codebase Audit" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fix Priority" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Test Findings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.1 Session Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan Comparison" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -156,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -249,6 +250,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -614,6 +618,2306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VarsityHub — Spiderweb v2 (Apr 15, 2026) — 4-agent deep audit + triage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>4 parallel agents covered: onboarding/coach tools, payments, content lifecycle, cross-cutting infra. Findings triaged: real bugs FIXED in pass 8, false positives marked, decisions deferred where product input needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>File:Line</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Action Taken</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>ONBOARDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Approved-fan→coach transition fire-and-forget</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>AuthProvider.tsx:536-551</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Logic intentionally fire-and-forget for UX. Failure logs to Sentry. AuthProvider re-routes correctly on next checkAuth. Acceptable.</t>
+        </is>
+      </c>
+      <c r="G6" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>create-team success path: no fallback if API returns malformed team</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>app/(tabs)/create-team.tsx:533</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Edge case: malformed API response leaves user stuck. Low likelihood (server-controlled response).</t>
+        </is>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>manage-teams empty-state UI when API returns []</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>app/(tabs)/manage-teams.tsx:92-96</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>UX issue. Empty state could be more helpful but does have a "Create your first team" CTA.</t>
+        </is>
+      </c>
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>pending-approval: completeOnboarding could time out</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>app/onboarding/pending-approval.tsx:71-117</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Already awaited (L71), has 2-tier fallback (L102), shows retry UI on full failure (L118-123). Agent missed.</t>
+        </is>
+      </c>
+      <c r="G9" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Subscription paywall ↔ coach-agreement loop possible</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>AuthProvider.tsx:577-582</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Edge case: requires payment_pending flag stale + browser-close. Hard to reproduce.</t>
+        </is>
+      </c>
+      <c r="G10" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>edit-organization permission check race window</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>app/edit-organization.tsx:64-79</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Form rendered for ~2s before permission check completes. User can attempt edit but server 403s.</t>
+        </is>
+      </c>
+      <c r="G11" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>team-invite double-tap accept</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>app/team-invites.tsx:24-51</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Standard double-tap concern. Server should be idempotent on accept (check existing membership).</t>
+        </is>
+      </c>
+      <c r="G12" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>manage-users no team-grouping in UI</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>app/manage-users.tsx:30</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>TRUE (UX)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Confusing for coaches managing multiple teams. Cosmetic.</t>
+        </is>
+      </c>
+      <c r="G13" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>PAYMENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="75" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Ad refund on admin reject — money kept by VarsityHub</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/approvalService.ts:394</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>TRUE — REVENUE LOSS</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Now refunds via Stripe when paid ad is rejected. TransactionLog updated with refund metadata. payment_status set to refunded/refund_pending.</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="75" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Stripe charge.refunded webhook NOT handled</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts (no handler)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>TRUE — REVENUE LOSS</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Added handler for charge.refunded + charge.dispute.created. Marks tx REFUNDED, downgrades subscription users to rookie, releases ad reservations.</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="75" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Apple IAP grace period — no expiry check</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts:3027 (S2S handler)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>TRUE — REVENUE LOSS</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Now sets grace_period_expires_at on DID_FAIL_TO_RENEW. requireOnboarded checks it and lazy-downgrades expired-grace users.</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="75" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Plan downgrade max_teams enforcement absent</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts:2296-2298</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>After downgrade Veteran→Rookie, user keeps all previous teams. max_teams updated but team count not enforced.</t>
+        </is>
+      </c>
+      <c r="G18" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED — needs product call: hard delete vs lazy block</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="75" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Orphan payments if finalizeFromSession throws</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts:2221</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Pass 4 already added NEEDS_REVIEW marking on session re-verify failure. Other failure paths still possible but rare.</t>
+        </is>
+      </c>
+      <c r="G19" s="36" t="inlineStr">
+        <is>
+          <t>PARTIAL FIX (pass 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Apple IAP restore-purchase endpoint missing</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>No /payments/restore-purchase exists</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Users reinstalling app must re-purchase. UX issue not security/billing.</t>
+        </is>
+      </c>
+      <c r="G20" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="75" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Ad slot double-booking under concurrent payment</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/payments.ts:1334</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Serializable isolation handles same-ad concurrent. Different ads on same date/zip still possible. Auto-refund SLOT_FULL handles it.</t>
+        </is>
+      </c>
+      <c r="G21" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG (compensating control exists)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="75" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>No /subscription/reactivate (un-cancel) endpoint</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>No endpoint exists</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>TRUE — UX gap</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Standard Stripe pattern: cancel_at_period_end can be reverted before period end. Not implemented.</t>
+        </is>
+      </c>
+      <c r="G22" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="75" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Banned users could comment + post (DM-only block)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/posts.ts:1069 + 574</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Added banned check at both POST /posts and POST /posts/:id/comments — symmetric with existing DM block.</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="75" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Story expiry has no cron job / fallback cleanup</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/gameStories.ts:119</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Stories filtered by expires_at in queries; if query missing the filter, expired stories show. Cron job for hard-delete missing.</t>
+        </is>
+      </c>
+      <c r="G25" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED — needs cron infra setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="75" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Game story geofence uses client-supplied coords</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/geofencing.ts:138-213</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Server trusts userLat/userLon from client. Spoofable. Need to verify against IP geolocation or device attestation.</t>
+        </is>
+      </c>
+      <c r="G26" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED — needs anti-spoof strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="75" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>RSVP capacity race condition (concurrent RSVPs)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/events.ts:432-446</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Capacity check inside tx but doesn't account for concurrent inserts. Need DB-level CHECK or unique counter.</t>
+        </is>
+      </c>
+      <c r="G27" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED — needs schema/index change</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="75" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Event cancellation: push fail → user not notified</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/events.ts:1065-1087</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Email removed from cancellation flow; push only. If push fails, no fallback.</t>
+        </is>
+      </c>
+      <c r="G28" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="75" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Group chat: no member-removal endpoint</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/group-chats.ts</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Added DELETE /group-chats/:chatId/members/:userId. Self-leave + creator-removes-member supported. Last-creator-out deletes the chat.</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="75" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Block: bidirectional follow already handled</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/users.ts:1192-1199</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Already deletes follows in both directions on block. Agent missed.</t>
+        </is>
+      </c>
+      <c r="G30" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="75" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>@mention TOCTOU: banned-between-parse-and-notify</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/mentionNotifications.ts:34</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Tiny window. Banned user receives stale notification.</t>
+        </is>
+      </c>
+      <c r="G31" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="75" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Pin-post check stale-membership race</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/posts.ts:63-87</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Theoretical race; isCoachOfPostTeam re-checks on every pin attempt.</t>
+        </is>
+      </c>
+      <c r="G32" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="75" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Private profile direct-URL access not unit-tested</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/posts.ts:970-975</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Privacy check (isAuthorHiddenFromViewer) IS called. Test coverage gap, not a bug.</t>
+        </is>
+      </c>
+      <c r="G33" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="75" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Report rate limiter — verify config</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>server/src/middleware/rateLimiters.ts</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>reportLimiter exists at lines 116-120, applied at reports.ts:57. Working.</t>
+        </is>
+      </c>
+      <c r="G34" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>PRIVACY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="75" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Search reveals blocked users by exact username</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/search.ts:25</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Excluded blocked users from search results (both directions of block). Verified at L29.</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>SECURITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="75" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Push token re-registration on every login</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>context/AuthProvider.tsx:293</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>sign-in.tsx + AuthProvider both call registerPushToken. Edge case: web/Apple/Google sign-in paths may not. Tests required.</t>
+        </is>
+      </c>
+      <c r="G38" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="75" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Moderation count via JSON string-matching</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/moderation.ts:82-107</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Counter uses contains:userId on JSON. Schema change to use FK relation needed for correctness.</t>
+        </is>
+      </c>
+      <c r="G39" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED — needs schema migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="75" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Password change does NOT invalidate access JWTs (only refresh)</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/auth.ts:855-858</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Refresh tokens deleted; JWTs valid until expiry (~15 min). Need token_rotation_id versioning to invalidate immediately.</t>
+        </is>
+      </c>
+      <c r="G40" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED — needs JWT scheme change</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="75" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>CORS allows requests with no origin</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>server/src/app.ts:120-122</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Mobile apps + native clients have no Origin header — disabling no-origin would break the app. Acceptable for read endpoints; consider tightening for state-changing methods.</t>
+        </is>
+      </c>
+      <c r="G41" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG (intentional for mobile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="75" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Health endpoint reveals integration status</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/health.ts:20</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Detail only behind X-Health-Check-Secret. Public /health returns {status:ok}. Working as designed.</t>
+        </is>
+      </c>
+      <c r="G42" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="75" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Sentry sends user_id + email (PII)</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>utils/sentry.ts:74-81</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>TRUE — PRIVACY</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Need to scrub or hash user identifiers before sending to Sentry. Compliance issue.</t>
+        </is>
+      </c>
+      <c r="G43" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED — needs PII review</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="75" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Admin transaction lookup by sessionId</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/admin.ts:387</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Stripe session IDs are random 24-char strings — not enumerable. Endpoint also requireAdmin.</t>
+        </is>
+      </c>
+      <c r="G44" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>PRIVACY</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="75" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Username change doesn't update mentions</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/auth.ts:1100</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>TRUE — UX</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Old @username mentions become stale. Could rename or mark stale on change.</t>
+        </is>
+      </c>
+      <c r="G46" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="75" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Privacy toggle only affects future posts</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/auth.ts:1256</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>TRUE — UX</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Existing posts stay public. Need bulk-update endpoint or document the limitation.</t>
+        </is>
+      </c>
+      <c r="G47" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="75" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Account deletion message orphan handling</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/users.ts:622</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Sent messages deleted; recipient still has copy. Standard messaging-platform pattern.</t>
+        </is>
+      </c>
+      <c r="G48" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="75" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Search enumeration via 1-char queries</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/search.ts:15</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Rate-limited per IP. Determined attacker with proxies could enumerate but it's noisy.</t>
+        </is>
+      </c>
+      <c r="G49" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>RELIABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="75" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Notification deep link mapping incomplete</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>utils/deepLinks.ts:81</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>New notification types may not have routes. Add type-completeness test.</t>
+        </is>
+      </c>
+      <c r="G51" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="75" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Theme/blocked-list not server-synced</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>AsyncStorage settings</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Some settings (DM policy, notif prefs) sync via /me/preferences. Theme + blocked list are server-side already.</t>
+        </is>
+      </c>
+      <c r="G52" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="75" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Geocoding fallback strategy unverified</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/geocoding.ts</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Pass 3 added retry on OVER_QUERY_LIMIT. Cache TTL reduced to 24h. Working.</t>
+        </is>
+      </c>
+      <c r="G53" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="75" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Moderation thresholds hardcoded</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>server/src/lib/moderation.ts:12-15</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>TRUE — Ops</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Should be env-vars or DB config for tuning at scale. Not blocking.</t>
+        </is>
+      </c>
+      <c r="G55" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="75" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Mention search rate limit verification</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>server/src/routes/users.ts:76</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>mentionsSearchLimiter applied via middleware chain. Working.</t>
+        </is>
+      </c>
+      <c r="G56" s="36" t="inlineStr">
+        <is>
+          <t>NOT-A-BUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="75" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Rate-limit env unified parser silent bypass</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>server/src/middleware/rateLimiters.ts:22</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL TRUE</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>isTruthyEnv accepts 1/true/yes/on. Set in Railway = global disable. Should log when bypassing.</t>
+        </is>
+      </c>
+      <c r="G57" s="36" t="inlineStr">
+        <is>
+          <t>DEFERRED — log enhancement</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A23:G23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>VarsityHub Subscription Plan Comparison (Updated Apr 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Feature / Limit</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rookie (Free)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Veteran ($0.99/mo/team)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Legend ($29.99/yr)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Accurate?</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Your Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>$0.99/mo per team over 2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>$29.99/year (first 100: $14.99)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CORRECTED: $0.99 not $1.00. payments.ts L234: unit_amount=99 cents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Max Teams Owned</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Unlimited (3+ billable)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Max Authorized Users Per Team</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Max Roster Size Per Team</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Org Auth User Strategy</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fixed 1 user</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 per team</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Community Events (pending)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8 pending max</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unlimited </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Wrong → Fixed</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALL FAN EVENTS HAVE TO GO THROUGH THE SAME APPROVAL PROCESS NO MATTER WAT TIER THE COACH IS </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Extracurricular Teams</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Yes (Theater, Chess, Debate, etc.)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ad Slot Booking</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Wrong → Fixed</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CORRECTED: Ad creation requires Veteran/Legend plan or admin. ads.ts L114-122: 403 PLAN_REQUIRED for Rookie users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ad Pricing</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>$4.99/wk weekday, $7.99/wk weekend</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ad Radius</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10km</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10km</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10km</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Apple IAP Product ID</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MIDTIER</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TOPTIER / 6761790811</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DB/Store Verify</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code mapping exists (payments.ts L2341) but live product IDs need App Store Connect verification. MAKE SURE THESE WORKS ALL VALUES ARE ALREADY ACCURATE </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Promo Code</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FIRST100 (50% off, max 100)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DB/Store Verify</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PromoCode table and route exist. Exact code and discount are DB runtime values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>All Core Features (feed, DM, search)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Message History</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>50 per request (paginated)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>50 per request (paginated)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>50 per request (paginated)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Wrong → Fixed</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CORRECTED: No "300" limit in code. messages.ts L62: Math.min(..., 50) hard cap per API call. Paginated with cursor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Moderation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3 warn, 5 strike, 8 suspend, 12 ban</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Wrong → Fixed</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CORRECTED: moderation.ts L12-15 thresholds are 3/5/8/12, not 1/2/3.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1527,7 +3831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2592,7 +4896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4288,7 +6592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4802,7 +7106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5114,7 +7418,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5301,7 +7605,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5377,7 +7681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17410,497 +19714,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>VarsityHub Subscription Plan Comparison (Updated Apr 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Feature / Limit</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Rookie (Free)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Veteran ($0.99/mo/team)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Legend ($29.99/yr)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Accurate?</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Your Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>$0.99/mo per team over 2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>$29.99/year (first 100: $14.99)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CORRECTED: $0.99 not $1.00. payments.ts L234: unit_amount=99 cents.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Max Teams Owned</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Unlimited (3+ billable)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Max Authorized Users Per Team</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Max Roster Size Per Team</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Org Auth User Strategy</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Fixed 1 user</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5 per team</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Community Events (pending)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>8 pending max</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unlimited </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Wrong → Fixed</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALL FAN EVENTS HAVE TO GO THROUGH THE SAME APPROVAL PROCESS NO MATTER WAT TIER THE COACH IS </t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Extracurricular Teams</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Yes (Theater, Chess, Debate, etc.)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ad Slot Booking</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Wrong → Fixed</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CORRECTED: Ad creation requires Veteran/Legend plan or admin. ads.ts L114-122: 403 PLAN_REQUIRED for Rookie users.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ad Pricing</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>$4.99/wk weekday, $7.99/wk weekend</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Ad Radius</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10km</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>10km</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>10km</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Apple IAP Product ID</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MIDTIER</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TOPTIER / 6761790811</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>DB/Store Verify</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code mapping exists (payments.ts L2341) but live product IDs need App Store Connect verification. MAKE SURE THESE WORKS ALL VALUES ARE ALREADY ACCURATE </t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Promo Code</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>FIRST100 (50% off, max 100)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>DB/Store Verify</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>PromoCode table and route exist. Exact code and discount are DB runtime values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>All Core Features (feed, DM, search)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Message History</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>50 per request (paginated)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>50 per request (paginated)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>50 per request (paginated)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Wrong → Fixed</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CORRECTED: No "300" limit in code. messages.ts L62: Math.min(..., 50) hard cap per API call. Paginated with cursor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Moderation</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3 warn, 5 strike, 8 suspend, 12 ban</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Wrong → Fixed</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CORRECTED: moderation.ts L12-15 thresholds are 3/5/8/12, not 1/2/3.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>